--- a/iivw/demo/iivw_results.xlsx
+++ b/iivw/demo/iivw_results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="271" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="271" uniqueCount="139">
   <si>
     <t>IIVW diagnostic model comparison</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Unweighted</t>
   </si>
   <si>
-    <t>_r_b</t>
+    <t>Coef.</t>
   </si>
   <si>
     <t>0.32</t>
@@ -329,9 +329,6 @@
   </si>
   <si>
     <t>Model</t>
-  </si>
-  <si>
-    <t>Coef.</t>
   </si>
   <si>
     <t>0.37</t>
@@ -1442,7 +1439,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>105</v>
+        <v>16</v>
       </c>
       <c r="D3" s="29" t="s">
         <v>28</v>
@@ -1459,13 +1456,13 @@
         <v>97</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E4" s="48" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5">
@@ -1482,7 +1479,7 @@
         <v>33</v>
       </c>
       <c r="E5" s="48" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6">
@@ -1493,13 +1490,13 @@
         <v>7</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D6" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E6" s="48" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7">
@@ -1510,13 +1507,13 @@
         <v>8</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D7" s="47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E7" s="48" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8">
@@ -1527,13 +1524,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D8" s="47" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E8" s="48" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9">
@@ -1544,13 +1541,13 @@
         <v>10</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D9" s="47" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E9" s="48" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10">
@@ -1578,13 +1575,13 @@
         <v>5</v>
       </c>
       <c r="C11" s="47" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D11" s="47" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E11" s="48" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -1595,10 +1592,10 @@
         <v>98</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D12" s="47" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E12" s="48" t="s">
         <v>42</v>
@@ -1612,10 +1609,10 @@
         <v>99</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D13" s="47" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E13" s="48" t="s">
         <v>42</v>
@@ -1629,10 +1626,10 @@
         <v>100</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D14" s="47" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E14" s="48" t="s">
         <v>42</v>
@@ -1649,10 +1646,10 @@
         <v>22</v>
       </c>
       <c r="D15" s="47" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E15" s="48" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16">
@@ -1663,13 +1660,13 @@
         <v>102</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D16" s="47" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E16" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17">
@@ -1683,10 +1680,10 @@
         <v>67</v>
       </c>
       <c r="D17" s="47" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E17" s="48" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18">
@@ -1697,10 +1694,10 @@
         <v>13</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D18" s="47" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E18" s="48" t="s">
         <v>42</v>
@@ -1714,7 +1711,7 @@
         <v>14</v>
       </c>
       <c r="C19" s="46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D19" s="45" t="s">
         <v>1</v>
